--- a/رصيد بداية المدة.xlsx
+++ b/رصيد بداية المدة.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Tools\الحركة اليومية لفواتير السائح\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ireac\Documents\GitHub\MZ.S-ERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C853F554-4728-4F6B-8B8D-B55F102C2779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B013F1FB-2EE9-4C76-AAA3-D6A67E9BF652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="110">
   <si>
     <t>اسم الصنف</t>
   </si>
@@ -340,9 +340,6 @@
   </si>
   <si>
     <t>كروت نامي لحم (معدل وراثي)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">قطع غيار / معدات صيانة </t>
   </si>
   <si>
     <t>مرتجع</t>
@@ -778,7 +775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.796875" customWidth="1"/>
@@ -2429,16 +2426,16 @@
     </row>
     <row r="92" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B92" s="1">
         <v>133000.1</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E92" s="2">
         <v>0</v>
@@ -2447,16 +2444,16 @@
     </row>
     <row r="93" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B93" s="1">
         <v>133000.20000000001</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E93" s="2">
         <v>0</v>
@@ -2465,43 +2462,25 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B94" s="1">
+        <v>133000.4</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B94" s="1">
-        <v>133000.29999999999</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="D94" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E94" s="2">
         <v>0</v>
       </c>
       <c r="F94" s="1"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B95" s="1">
-        <v>133000.4</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E95" s="2">
-        <v>0</v>
-      </c>
-      <c r="F95" s="1"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="C92:C95">
-    <cfRule type="uniqueValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="C92:C94">
+    <cfRule type="uniqueValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
